--- a/src/test/resources/Payload.xlsx
+++ b/src/test/resources/Payload.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\signity\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56DF475B-E926-433D-B175-5BB0CA13FAF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA36A031-5384-40C4-998B-9227665A13BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
   <si>
     <t>merchantId</t>
   </si>
@@ -51,61 +51,61 @@
     <t>isDfs</t>
   </si>
   <si>
-    <t>https://track.go2cloud.org</t>
-  </si>
-  <si>
-    <t>https://server.nginx.com</t>
-  </si>
-  <si>
-    <t>https://email.example.com</t>
-  </si>
-  <si>
-    <t>https://bucket.amazonaws.com</t>
-  </si>
-  <si>
-    <t>https://jira.company.com</t>
-  </si>
-  <si>
-    <t>https://track.go2jump.org</t>
-  </si>
-  <si>
-    <t>https://example.domains</t>
-  </si>
-  <si>
-    <t>https://hhhh.example.com</t>
-  </si>
-  <si>
-    <t>https://test-a-tag.com</t>
-  </si>
-  <si>
-    <t>https://mail.example.com</t>
-  </si>
-  <si>
-    <t>https://web-1.example.com</t>
-  </si>
-  <si>
-    <t>https://www.googletagmanager.com</t>
-  </si>
-  <si>
-    <t>https://keep.google.com</t>
-  </si>
-  <si>
-    <t>https://pagead.googleadservices.com</t>
-  </si>
-  <si>
-    <t>https://track.fintelconnect.com</t>
-  </si>
-  <si>
-    <t>https://bit.ly</t>
-  </si>
-  <si>
-    <t>https://mysite.pantheonsite.io</t>
-  </si>
-  <si>
-    <t>https://us1.list-manage.com</t>
-  </si>
-  <si>
-    <t>https://stage.example.com</t>
+    <t>https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Category:Artificial_intelligence</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search</t>
+  </si>
+  <si>
+    <t>HTTP://EXAMPL.COM:80/</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/C%2B%2B</t>
+  </si>
+  <si>
+    <t>https://www.buzzfeed.com/ca</t>
+  </si>
+  <si>
+    <t>https://globo.com</t>
+  </si>
+  <si>
+    <t>https://www.hsbc.com/</t>
+  </si>
+  <si>
+    <t>https://theinformr.com</t>
+  </si>
+  <si>
+    <t>https://simplerate.ca</t>
+  </si>
+  <si>
+    <t>https://atila.ca</t>
+  </si>
+  <si>
+    <t>https://apnews.com/</t>
+  </si>
+  <si>
+    <t>https://moneyeh.ca/</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/w/index.php?search=machine+learning</t>
+  </si>
+  <si>
+    <t>https://a.com?b=2&amp;a=1</t>
+  </si>
+  <si>
+    <t>https://crawldemolinksnew.signitydemo.in</t>
+  </si>
+  <si>
+    <t>https://www.save.ca/flyers/</t>
   </si>
 </sst>
 </file>
@@ -437,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -479,16 +479,16 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="b">
         <v>1</v>
@@ -502,16 +502,16 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3" t="b">
         <v>1</v>
@@ -525,16 +525,16 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -548,16 +548,16 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -571,16 +571,16 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="b">
         <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="b">
         <v>1</v>
@@ -594,16 +594,16 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" t="b">
         <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="b">
         <v>1</v>
@@ -617,16 +617,16 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="b">
         <v>1</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
         <v>1</v>
@@ -637,19 +637,19 @@
         <v>6</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9" t="b">
         <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="b">
         <v>1</v>
@@ -660,19 +660,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="b">
         <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="b">
         <v>1</v>
@@ -683,19 +683,19 @@
         <v>6</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11" t="b">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -706,7 +706,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>1</v>
@@ -718,7 +718,7 @@
         <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>6</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C13">
         <v>1</v>
@@ -741,7 +741,7 @@
         <v>1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="b">
         <v>1</v>
@@ -752,7 +752,7 @@
         <v>6</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C14">
         <v>1</v>
@@ -764,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="F14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="b">
         <v>1</v>
@@ -775,7 +775,7 @@
         <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>1</v>
@@ -787,7 +787,7 @@
         <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>6</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
         <v>1</v>
@@ -821,7 +821,7 @@
         <v>6</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -833,7 +833,7 @@
         <v>1</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="b">
         <v>1</v>
@@ -844,7 +844,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -856,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -867,7 +867,7 @@
         <v>6</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -879,7 +879,7 @@
         <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
         <v>1</v>
@@ -890,7 +890,7 @@
         <v>6</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -902,9 +902,32 @@
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -917,18 +940,13 @@
     <hyperlink ref="B6" r:id="rId5" xr:uid="{09A96C53-54DF-49BB-8A29-07507E0024EC}"/>
     <hyperlink ref="B7" r:id="rId6" xr:uid="{B62584E6-E555-4A86-A1B9-C92B9B85781E}"/>
     <hyperlink ref="B8" r:id="rId7" xr:uid="{E70FA916-4086-4F64-A6B2-81A78A4DBCC8}"/>
-    <hyperlink ref="B9" r:id="rId8" xr:uid="{6979D950-46EB-488C-8406-9D0F0C66923C}"/>
-    <hyperlink ref="B10" r:id="rId9" xr:uid="{1409DB28-0D77-4122-B86A-748A2F982400}"/>
-    <hyperlink ref="B11" r:id="rId10" xr:uid="{F9E48A46-1485-4095-8000-468A2CB7042C}"/>
-    <hyperlink ref="B12" r:id="rId11" xr:uid="{4B367B40-9819-45CA-9F24-F20FAF1E348E}"/>
-    <hyperlink ref="B13" r:id="rId12" xr:uid="{1A8C52D9-1898-40CB-BDD8-5CBA7C7EA2AB}"/>
-    <hyperlink ref="B14" r:id="rId13" xr:uid="{BD1A9F6D-F10B-4B5D-95B8-90642762AC11}"/>
-    <hyperlink ref="B15" r:id="rId14" xr:uid="{4EE4B5B0-2F24-462D-8316-FECED14F36C6}"/>
-    <hyperlink ref="B16" r:id="rId15" xr:uid="{15833D9A-4F5E-4A73-90A4-C285878080C9}"/>
-    <hyperlink ref="B17" r:id="rId16" xr:uid="{C9D10055-62C7-4098-90BC-55F2DEFDC38B}"/>
-    <hyperlink ref="B18" r:id="rId17" xr:uid="{0F6E2813-489A-487F-A1F0-86DDFDEA518B}"/>
-    <hyperlink ref="B19" r:id="rId18" xr:uid="{19A8169E-9238-4B64-835E-75D70EF90AFD}"/>
-    <hyperlink ref="B20" r:id="rId19" xr:uid="{9E94A8E6-5AF3-4252-A27D-C9E46D65D871}"/>
+    <hyperlink ref="B12" r:id="rId8" xr:uid="{5BACB4C7-4DCB-40BB-BC29-7E98A3B2B83D}"/>
+    <hyperlink ref="B13" r:id="rId9" xr:uid="{A052D562-DBE1-4A5B-A09F-109B8FC7E9DC}"/>
+    <hyperlink ref="B14" r:id="rId10" xr:uid="{9E6AEF40-9E64-47B7-9DD5-C25586F9C02B}"/>
+    <hyperlink ref="B9" r:id="rId11" xr:uid="{B753610A-6108-456F-BA19-52B0FD72BCAD}"/>
+    <hyperlink ref="B10" r:id="rId12" xr:uid="{20594C5C-8531-4C27-941F-863486FAD9E4}"/>
+    <hyperlink ref="B21" r:id="rId13" xr:uid="{1A032DBF-5357-4A9D-8A1D-51EA69B46A60}"/>
+    <hyperlink ref="B11" r:id="rId14" xr:uid="{D9481C45-4C06-4BE5-B812-D8E8FFF79B20}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/test/resources/Payload.xlsx
+++ b/src/test/resources/Payload.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\signity\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\signity\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA36A031-5384-40C4-998B-9227665A13BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5532871E-C8B9-49AB-8909-96D2FFA084D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="28">
   <si>
     <t>merchantId</t>
   </si>
@@ -51,79 +51,74 @@
     <t>isDfs</t>
   </si>
   <si>
-    <t>https://en.wikipedia.org/wiki/Category:Machine_learning_algorithms</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Category:Artificial_intelligence</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Special:Search?search=Machine%20Learning</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/w/index.php?search=Research&amp;title=Special:Search</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/w/index.php?search=Java_(programming_language)&amp;title=Special:Search</t>
-  </si>
-  <si>
-    <t>HTTP://EXAMPL.COM:80/</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/C%2B%2B</t>
-  </si>
-  <si>
-    <t>https://www.buzzfeed.com/ca</t>
-  </si>
-  <si>
-    <t>https://globo.com</t>
-  </si>
-  <si>
-    <t>https://www.hsbc.com/</t>
-  </si>
-  <si>
-    <t>https://theinformr.com</t>
-  </si>
-  <si>
-    <t>https://simplerate.ca</t>
-  </si>
-  <si>
-    <t>https://atila.ca</t>
-  </si>
-  <si>
-    <t>https://apnews.com/</t>
-  </si>
-  <si>
-    <t>https://moneyeh.ca/</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/w/index.php?search=machine+learning</t>
-  </si>
-  <si>
-    <t>https://a.com?b=2&amp;a=1</t>
-  </si>
-  <si>
-    <t>https://crawldemolinksnew.signitydemo.in</t>
-  </si>
-  <si>
-    <t>https://www.save.ca/flyers/</t>
+    <t>https://earnandburn.ca</t>
+  </si>
+  <si>
+    <t>https://familytaxrecovery.ca</t>
+  </si>
+  <si>
+    <t>https://feeds.buzzsprout.co</t>
+  </si>
+  <si>
+    <t>https://finances.ca</t>
+  </si>
+  <si>
+    <t>https://financebuzz.com</t>
+  </si>
+  <si>
+    <t>https://fintechlabs.com</t>
+  </si>
+  <si>
+    <t>https://finanso.com</t>
+  </si>
+  <si>
+    <t>https://forums.redflagdeals.com</t>
+  </si>
+  <si>
+    <t>https://flyers.smartcanucks.ca</t>
+  </si>
+  <si>
+    <t>https://fnbo.com</t>
+  </si>
+  <si>
+    <t>https://forbes.com</t>
+  </si>
+  <si>
+    <t>https://frugalflyer.ca</t>
+  </si>
+  <si>
+    <t>https://georgeneufeld.ca</t>
+  </si>
+  <si>
+    <t>https://genymoney.ca</t>
+  </si>
+  <si>
+    <t>https://go.movingwaldo.ca</t>
+  </si>
+  <si>
+    <t>https://go.myratecompass.ca</t>
+  </si>
+  <si>
+    <t>https://greatcanadianrebates.ca</t>
+  </si>
+  <si>
+    <t>https://greenfi.co</t>
+  </si>
+  <si>
+    <t>https://hellosafe.ca</t>
+  </si>
+  <si>
+    <t>https://highinterestsavings.ca</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -146,19 +141,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -475,7 +464,7 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>8</v>
       </c>
       <c r="C2">
@@ -498,7 +487,7 @@
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
       <c r="C3">
@@ -521,7 +510,7 @@
       <c r="A4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>10</v>
       </c>
       <c r="C4">
@@ -544,7 +533,7 @@
       <c r="A5" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>11</v>
       </c>
       <c r="C5">
@@ -567,7 +556,7 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6">
@@ -590,7 +579,7 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>13</v>
       </c>
       <c r="C7">
@@ -613,7 +602,7 @@
       <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>14</v>
       </c>
       <c r="C8">
@@ -636,8 +625,8 @@
       <c r="A9" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>23</v>
+      <c r="B9" t="s">
+        <v>15</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -659,8 +648,8 @@
       <c r="A10" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
+      <c r="B10" t="s">
+        <v>16</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -682,8 +671,8 @@
       <c r="A11" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>26</v>
+      <c r="B11" t="s">
+        <v>17</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -705,14 +694,14 @@
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>15</v>
+      <c r="B12" t="s">
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -728,14 +717,14 @@
       <c r="A13" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>16</v>
+      <c r="B13" t="s">
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="b">
         <v>1</v>
@@ -751,14 +740,14 @@
       <c r="A14" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>17</v>
+      <c r="B14" t="s">
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" t="b">
         <v>1</v>
@@ -774,14 +763,14 @@
       <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>18</v>
+      <c r="B15" t="s">
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" t="b">
         <v>1</v>
@@ -797,14 +786,14 @@
       <c r="A16" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
+      <c r="B16" t="s">
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" t="b">
         <v>1</v>
@@ -820,14 +809,14 @@
       <c r="A17" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>20</v>
+      <c r="B17" t="s">
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -843,14 +832,14 @@
       <c r="A18" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>21</v>
+      <c r="B18" t="s">
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
@@ -866,14 +855,14 @@
       <c r="A19" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>22</v>
+      <c r="B19" t="s">
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -889,14 +878,14 @@
       <c r="A20" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>15</v>
+      <c r="B20" t="s">
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -912,14 +901,14 @@
       <c r="A21" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>25</v>
+      <c r="B21" t="s">
+        <v>27</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
@@ -932,22 +921,6 @@
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{EA9EDB7E-6AD2-453C-BDD2-FEF9FB9554D3}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{231280E6-BB38-45C7-938D-AB1DC8D0F5EA}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{F2999BD7-6568-4E87-8812-46DA834AA1F9}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{14CFD087-3E4C-45B8-86C6-CAE589232BFA}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{09A96C53-54DF-49BB-8A29-07507E0024EC}"/>
-    <hyperlink ref="B7" r:id="rId6" xr:uid="{B62584E6-E555-4A86-A1B9-C92B9B85781E}"/>
-    <hyperlink ref="B8" r:id="rId7" xr:uid="{E70FA916-4086-4F64-A6B2-81A78A4DBCC8}"/>
-    <hyperlink ref="B12" r:id="rId8" xr:uid="{5BACB4C7-4DCB-40BB-BC29-7E98A3B2B83D}"/>
-    <hyperlink ref="B13" r:id="rId9" xr:uid="{A052D562-DBE1-4A5B-A09F-109B8FC7E9DC}"/>
-    <hyperlink ref="B14" r:id="rId10" xr:uid="{9E6AEF40-9E64-47B7-9DD5-C25586F9C02B}"/>
-    <hyperlink ref="B9" r:id="rId11" xr:uid="{B753610A-6108-456F-BA19-52B0FD72BCAD}"/>
-    <hyperlink ref="B10" r:id="rId12" xr:uid="{20594C5C-8531-4C27-941F-863486FAD9E4}"/>
-    <hyperlink ref="B21" r:id="rId13" xr:uid="{1A032DBF-5357-4A9D-8A1D-51EA69B46A60}"/>
-    <hyperlink ref="B11" r:id="rId14" xr:uid="{D9481C45-4C06-4BE5-B812-D8E8FFF79B20}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>